--- a/Matrix metabo.xlsx
+++ b/Matrix metabo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viriginie\OneDrive - Universite de Liege\Documents\THESE VIRGINIE MAI 2023\projet article\DISSERTATION DOCTORALE\DOSSIER ARTICLE FIN THESE A SOUMETTRE\METABOLOMIC FOR PAPER\4Statistical analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FB6FEEB-9684-4B6F-A6C3-7845AB1E984D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFABF56-EE5E-433F-8AC9-46E96072ADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E4E79864-6BBB-4A78-BCA9-E2934A1A396E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="648">
   <si>
     <t>Shared name</t>
   </si>
@@ -1151,177 +1151,9 @@
     <t>845.4431799999999</t>
   </si>
   <si>
-    <t>741.8455</t>
-  </si>
-  <si>
-    <t>741.8454916206199</t>
-  </si>
-  <si>
-    <t>4.6388755</t>
-  </si>
-  <si>
-    <t>3.30863147822964</t>
-  </si>
-  <si>
-    <t>0.8226</t>
-  </si>
-  <si>
-    <t>51.5005</t>
-  </si>
-  <si>
-    <t>793.346</t>
-  </si>
-  <si>
-    <t>IUQRTVVZUXBHMO</t>
-  </si>
-  <si>
-    <t>euphodendroidin M</t>
-  </si>
-  <si>
-    <t>C[C@@]1(OC(C)=O)C[C@](O)(C([C@@H](C)/C=C/C(C)(C)[C@H](OC(C)=O)[C@H](OC(C)=O)[C@@H](OC(C(C)C)=O)C([C@@H]2OC(C(C)C)=O)=C)=O)[C@]2([H])[C@H]1OC(C3=CC=CC=C3)=O</t>
-  </si>
-  <si>
-    <t>278.33</t>
-  </si>
-  <si>
-    <t>288.0</t>
-  </si>
-  <si>
-    <t>Jatrophane diterpenoids</t>
-  </si>
-  <si>
-    <t>Diterpenoids</t>
-  </si>
-  <si>
     <t>Terpenoids</t>
   </si>
   <si>
-    <t>C=C1C(OC(=O)C(C)C)C(OC(C)=O)C(OC(C)=O)C(C)(C)C=CC(C)C(=O)C2(O)CC(C)(OC(C)=O)C(OC(=O)c3ccccc3)C2C1OC(=O)C(C)C</t>
-  </si>
-  <si>
-    <t>C41H54O14</t>
-  </si>
-  <si>
-    <t>770.351356408</t>
-  </si>
-  <si>
-    <t>1.33052686E8</t>
-  </si>
-  <si>
-    <t>[2,9,10-triacetyloxy-3a-hydroxy-2,5,8,8-tetramethyl-12-methylidene-11,13-bis(2-methylpropanoyloxy)-4-oxo-1,3,5,9,10,11,13,13a-octahydrocyclopenta[12]annulen-1-yl] benzoate</t>
-  </si>
-  <si>
-    <t>https://pubchem.ncbi.nlm.nih.gov/compound/133052686</t>
-  </si>
-  <si>
-    <t>0.16417910447761194</t>
-  </si>
-  <si>
-    <t>741.84549</t>
-  </si>
-  <si>
-    <t>CC1C=CC=C(C(=O)NC2=C(C(=O)C3=C(C2=O)C(=C(C4=C3C(=O)C(O4)(OC=CC(C(C(C(C5C(C1OC(O5)(C)C)C)C)OC(=O)C)C)OC)C)C)O)N6CCCC6)C</t>
-  </si>
-  <si>
-    <t>MassSpecGymID0379577</t>
-  </si>
-  <si>
-    <t>827.37</t>
-  </si>
-  <si>
-    <t>[M+Na]+</t>
-  </si>
-  <si>
-    <t>0.67466474</t>
-  </si>
-  <si>
-    <t>0.1937390466274687</t>
-  </si>
-  <si>
-    <t>COC1C=COC2(C)Oc3c(C)c(O)c4c(c3C2=O)C(=O)C(N2CCCC2)=C(NC(=O)C(C)=CC=CC(C)C2OC(C)(C)OC(C2C)C(C)C(OC(C)=O)C1C)C4=O</t>
-  </si>
-  <si>
-    <t>LCMBEQGDYIBKDI</t>
-  </si>
-  <si>
-    <t>C44H56N2O12</t>
-  </si>
-  <si>
-    <t>804.383325232</t>
-  </si>
-  <si>
-    <t>Polyketides</t>
-  </si>
-  <si>
-    <t>Macrolides</t>
-  </si>
-  <si>
-    <t>Ansa macrolides</t>
-  </si>
-  <si>
-    <t>3806604.0</t>
-  </si>
-  <si>
-    <t>(2-hydroxy-11-methoxy-3,7,12,14,17,17,20,24,32-nonamethyl-6,25,29,31-tetraoxo-28-pyrrolidin-1-yl-8,16,18,33-tetraoxa-26-azapentacyclo[25.3.1.14,7.115,19.05,30]tritriaconta-1(30),2,4,9,21,23,27-heptaen-13-yl) acetate</t>
-  </si>
-  <si>
-    <t>https://pubchem.ncbi.nlm.nih.gov/compound/3806604</t>
-  </si>
-  <si>
-    <t>85.52450999999996</t>
-  </si>
-  <si>
-    <t>1.126811158143744</t>
-  </si>
-  <si>
-    <t>0.10839872102007532</t>
-  </si>
-  <si>
-    <t>-5.209685476473987</t>
-  </si>
-  <si>
-    <t>0.047778968074902846</t>
-  </si>
-  <si>
-    <t>-6.33649663461773</t>
-  </si>
-  <si>
-    <t>0.009462994394211282</t>
-  </si>
-  <si>
-    <t>119.1608</t>
-  </si>
-  <si>
-    <t>368.07144</t>
-  </si>
-  <si>
-    <t>700.0971</t>
-  </si>
-  <si>
-    <t>1070.7358</t>
-  </si>
-  <si>
-    <t>1502.7341</t>
-  </si>
-  <si>
-    <t>523.6893</t>
-  </si>
-  <si>
-    <t>1631.605</t>
-  </si>
-  <si>
-    <t>94.644516</t>
-  </si>
-  <si>
-    <t>1167.47018</t>
-  </si>
-  <si>
-    <t>764.8407333333333</t>
-  </si>
-  <si>
-    <t>31.548171999999997</t>
-  </si>
-  <si>
     <t>483.139</t>
   </si>
   <si>
@@ -1604,261 +1436,18 @@
     <t>8524.015333333335</t>
   </si>
   <si>
-    <t>420.2943</t>
-  </si>
-  <si>
-    <t>420.29424101492395</t>
-  </si>
-  <si>
-    <t>7.5173006</t>
-  </si>
-  <si>
-    <t>2.97809462398852</t>
-  </si>
-  <si>
-    <t>Organic acids and derivatives</t>
-  </si>
-  <si>
-    <t>0.998</t>
-  </si>
-  <si>
-    <t>Carboxylic acids and derivatives</t>
-  </si>
-  <si>
-    <t>Alpha amino acids</t>
-  </si>
-  <si>
-    <t>0.913</t>
-  </si>
-  <si>
     <t>Fatty acids</t>
   </si>
   <si>
-    <t>Spingolipids</t>
-  </si>
-  <si>
-    <t>Sphingoid bases</t>
-  </si>
-  <si>
-    <t>0.6611</t>
-  </si>
-  <si>
-    <t>153.0698</t>
-  </si>
-  <si>
-    <t>420.2942</t>
-  </si>
-  <si>
-    <t>573.364</t>
-  </si>
-  <si>
-    <t>DXSMIOSVACQXTE</t>
-  </si>
-  <si>
-    <t>(3S,6R,12S)-6-benzyl-3-butan-2-yl-9-(6,7-dihydroxyoctyl)-1,4,7,10-tetrazabicyclo[10.4.0]hexadecane-2,5,8,11-tetrone</t>
-  </si>
-  <si>
-    <t>CCC(C)[C@@H]1NC(=O)[C@@H](CC2=CC=CC=C2)NC(=O)C(CCCCCC(O)C(C)O)NC(=O)[C@@H]3CCCCN3C1=O</t>
-  </si>
-  <si>
-    <t>451.04</t>
-  </si>
-  <si>
-    <t>571.0</t>
-  </si>
-  <si>
-    <t>Cyclic peptides</t>
-  </si>
-  <si>
-    <t>Oligopeptides</t>
-  </si>
-  <si>
-    <t>CCC(C)C1NC(=O)C(Cc2ccccc2)NC(=O)C(CCCCCC(O)C(C)O)NC(=O)C2CCCCN2C1=O</t>
-  </si>
-  <si>
-    <t>C31H48N4O6</t>
-  </si>
-  <si>
-    <t>572.3573852559999</t>
-  </si>
-  <si>
-    <t>7.5061206E7</t>
-  </si>
-  <si>
-    <t>6-benzyl-3-butan-2-yl-9-(6,7-dihydroxyoctyl)-1,4,7,10-tetrazabicyclo[10.4.0]hexadecane-2,5,8,11-tetrone</t>
-  </si>
-  <si>
-    <t>https://pubchem.ncbi.nlm.nih.gov/compound/75061206</t>
-  </si>
-  <si>
-    <t>0.11235955056179775</t>
-  </si>
-  <si>
-    <t>0.09411764705882353</t>
-  </si>
-  <si>
-    <t>420.29424</t>
-  </si>
-  <si>
-    <t>CCCCCC=CCC=CCCCCCCCC(=O)NC(CO)C(=O)O</t>
-  </si>
-  <si>
-    <t>MassSpecGymID0391588</t>
-  </si>
-  <si>
-    <t>368.28</t>
-  </si>
-  <si>
-    <t>0.5743088</t>
-  </si>
-  <si>
-    <t>0.3544324825202426</t>
-  </si>
-  <si>
-    <t>UQQXKOPWRCINAH</t>
-  </si>
-  <si>
-    <t>C21H37NO4</t>
-  </si>
-  <si>
-    <t>367.27225866399993</t>
-  </si>
-  <si>
     <t>Fatty amides</t>
   </si>
   <si>
     <t>N-acyl amines</t>
   </si>
   <si>
-    <t>7.494599E7</t>
-  </si>
-  <si>
-    <t>3-hydroxy-2-(octadeca-9,12-dienoylamino)propanoic acid</t>
-  </si>
-  <si>
-    <t>https://pubchem.ncbi.nlm.nih.gov/compound/74945990</t>
-  </si>
-  <si>
-    <t>52.01424000000003</t>
-  </si>
-  <si>
-    <t>0.19298245614035087</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>-247.086</t>
-  </si>
-  <si>
-    <t>132.22</t>
-  </si>
-  <si>
-    <t>C21H41NO7</t>
-  </si>
-  <si>
-    <t>C21H42NO7+</t>
-  </si>
-  <si>
-    <t>VIQCFIKPVOPVLI</t>
-  </si>
-  <si>
-    <t>InChI=1S/C21H41NO7/c22-18(20(24)25)17-29-19(23)15-13-11-9-7-5-3-1-2-4-6-8-10-12-14-16-21(26,27)28/h18,26-28H,1-17,22H2,(H,24,25)</t>
-  </si>
-  <si>
-    <t>(2S)-2-amino-3-(18,18,18-trihydroxyoctadecanoyloxy)propanoic acid</t>
-  </si>
-  <si>
-    <t>C(CCCCCCCCC(O)(O)O)CCCCCCCC(=O)OCC(C(=O)O)N</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>PUBCHEM:(139650361)</t>
-  </si>
-  <si>
-    <t>420.294</t>
-  </si>
-  <si>
-    <t>451.0</t>
-  </si>
-  <si>
-    <t>7.517</t>
-  </si>
-  <si>
-    <t>8.191733528991588e+17</t>
-  </si>
-  <si>
-    <t>8.188460461833897e+17</t>
-  </si>
-  <si>
-    <t>NC(COC(=O)CCCCCCCCCCCCCCCCC(O)(O)O)C(=O)O</t>
-  </si>
-  <si>
-    <t>419.2883026519999</t>
-  </si>
-  <si>
     <t>https://pubchem.ncbi.nlm.nih.gov/compound/0</t>
   </si>
   <si>
-    <t>-0.2859578514910372</t>
-  </si>
-  <si>
-    <t>0.6760899781515644</t>
-  </si>
-  <si>
-    <t>-4.254028425614183</t>
-  </si>
-  <si>
-    <t>0.03705698189265078</t>
-  </si>
-  <si>
-    <t>-3.968070574123146</t>
-  </si>
-  <si>
-    <t>0.04204947962906411</t>
-  </si>
-  <si>
-    <t>3240.722</t>
-  </si>
-  <si>
-    <t>9740.785</t>
-  </si>
-  <si>
-    <t>9367.56</t>
-  </si>
-  <si>
-    <t>5504.5283</t>
-  </si>
-  <si>
-    <t>34123.832</t>
-  </si>
-  <si>
-    <t>2949.489</t>
-  </si>
-  <si>
-    <t>28563.43</t>
-  </si>
-  <si>
-    <t>500.6272</t>
-  </si>
-  <si>
-    <t>178.3088</t>
-  </si>
-  <si>
-    <t>3116.9802</t>
-  </si>
-  <si>
-    <t>24142.68233333333</t>
-  </si>
-  <si>
-    <t>5940.525766666667</t>
-  </si>
-  <si>
-    <t>1265.3054</t>
-  </si>
-  <si>
     <t>376.2678</t>
   </si>
   <si>
@@ -2070,267 +1659,6 @@
   </si>
   <si>
     <t>958.0501733333334</t>
-  </si>
-  <si>
-    <t>275.1095</t>
-  </si>
-  <si>
-    <t>275.10949618180996</t>
-  </si>
-  <si>
-    <t>1.2152001</t>
-  </si>
-  <si>
-    <t>2.70701643902917</t>
-  </si>
-  <si>
-    <t>Organic 1,3-dipolar compounds</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>Allyl-type 1,3-dipolar organic compounds</t>
-  </si>
-  <si>
-    <t>0.757</t>
-  </si>
-  <si>
-    <t>Organic nitro compounds</t>
-  </si>
-  <si>
-    <t>0.717</t>
-  </si>
-  <si>
-    <t>0.702</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>0.509</t>
-  </si>
-  <si>
-    <t>0.4622</t>
-  </si>
-  <si>
-    <t>55.9965</t>
-  </si>
-  <si>
-    <t>219.113</t>
-  </si>
-  <si>
-    <t>PCYQRXYBKKZUSR</t>
-  </si>
-  <si>
-    <t>N-Formylcytisine CollisionEnergy:102040</t>
-  </si>
-  <si>
-    <t>O=CN1CC2CC(C1)c1cccc(=O)n1C2</t>
-  </si>
-  <si>
-    <t>72.91</t>
-  </si>
-  <si>
-    <t>78.0</t>
-  </si>
-  <si>
-    <t>Pyridine alkaloids; Quinolizidine alkaloids</t>
-  </si>
-  <si>
-    <t>Lysine alkaloids; Nicotinic acid alkaloids</t>
-  </si>
-  <si>
-    <t>C12H14N2O2</t>
-  </si>
-  <si>
-    <t>218.105527688</t>
-  </si>
-  <si>
-    <t>589870.0</t>
-  </si>
-  <si>
-    <t>6-oxo-7,11-diazatricyclo[7.3.1.02,7]trideca-2,4-diene-11-carbaldehyde</t>
-  </si>
-  <si>
-    <t>Cytisine, N-formyl-; 6-oxo-7,11-diazatricyclo[7.3.1.02,7]trideca-2,4-diene-11-carbaldehyde; CHEMBL1433686; DCA00706; NCGC00017402-02; NCGC00142626-01</t>
-  </si>
-  <si>
-    <t>https://pubchem.ncbi.nlm.nih.gov/compound/589870</t>
-  </si>
-  <si>
-    <t>0.0967741935483871</t>
-  </si>
-  <si>
-    <t>0.07246376811594203</t>
-  </si>
-  <si>
-    <t>C1=CC=C(C=C1)C2=NC3=C(N2)C=C(C=C3)S(=O)(=O)O</t>
-  </si>
-  <si>
-    <t>MassSpecGymID0025628</t>
-  </si>
-  <si>
-    <t>275.0485</t>
-  </si>
-  <si>
-    <t>20.0</t>
-  </si>
-  <si>
-    <t>0.5646987</t>
-  </si>
-  <si>
-    <t>0.9734252205616784</t>
-  </si>
-  <si>
-    <t>O=S(=O)(O)c1ccc2nc(-c3ccccc3)[nH]c2c1</t>
-  </si>
-  <si>
-    <t>UVCJGUGAGLDPAA</t>
-  </si>
-  <si>
-    <t>C13H10N2O3S</t>
-  </si>
-  <si>
-    <t>274.04121318</t>
-  </si>
-  <si>
-    <t>33919.0</t>
-  </si>
-  <si>
-    <t>2-phenyl-3H-benzimidazole-5-sulfonic acid</t>
-  </si>
-  <si>
-    <t>Ensulizole; 27503-81-7; 2-PHENYLBENZIMIDAZOLE-5-SULFONIC ACID; Phenylbenzimidazole sulfonic acid; ensulizol; 9YQ9DI1W42; DTXSID3038852; 1H-Benzimidazole-5-sulfonic acid-2-phenyl-; DTXCID1018852; 2-phenyl-1H-1,3-benzodiazole-6-sulfonic acid</t>
-  </si>
-  <si>
-    <t>https://pubchem.ncbi.nlm.nih.gov/compound/33919</t>
-  </si>
-  <si>
-    <t>0.0610000000000354</t>
-  </si>
-  <si>
-    <t>0.05714285714285714</t>
-  </si>
-  <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>-144.789</t>
-  </si>
-  <si>
-    <t>117.667</t>
-  </si>
-  <si>
-    <t>C8H14N6O5</t>
-  </si>
-  <si>
-    <t>C8H15N6O5+</t>
-  </si>
-  <si>
-    <t>PGVDNTIIUSWEDX</t>
-  </si>
-  <si>
-    <t>InChI=1S/C8H14N6O5/c1-4(11-5(9)10)19-8(16)14(18-3)6-12-7(15)13(6)17-2/h4H,1-3H3,(H4,9,10,11)</t>
-  </si>
-  <si>
-    <t>1-(diaminomethylideneamino)ethyl N-methoxy-N-(1-methoxy-4-oxo-1,3-diazet-2-yl)carbamate</t>
-  </si>
-  <si>
-    <t>CC(N=C(N)N)OC(=O)N(C1=NC(=O)N1OC)OC</t>
-  </si>
-  <si>
-    <t>-1.1</t>
-  </si>
-  <si>
-    <t>PUBCHEM:(88680875)</t>
-  </si>
-  <si>
-    <t>275.11</t>
-  </si>
-  <si>
-    <t>73.0</t>
-  </si>
-  <si>
-    <t>1.215</t>
-  </si>
-  <si>
-    <t>8.191513822831037e+17</t>
-  </si>
-  <si>
-    <t>8.188460031204682e+17</t>
-  </si>
-  <si>
-    <t>CON1C(=O)N=C1N(OC)C(=O)OC(C)N=C(N)N</t>
-  </si>
-  <si>
-    <t>274.102567548</t>
-  </si>
-  <si>
-    <t>8.8680875E7</t>
-  </si>
-  <si>
-    <t>SCHEMBL10866477</t>
-  </si>
-  <si>
-    <t>https://pubchem.ncbi.nlm.nih.gov/compound/88680875</t>
-  </si>
-  <si>
-    <t>0.8786612768340228</t>
-  </si>
-  <si>
-    <t>0.19245435794912322</t>
-  </si>
-  <si>
-    <t>-2.574607228582609</t>
-  </si>
-  <si>
-    <t>0.0451074181986767</t>
-  </si>
-  <si>
-    <t>-3.453268505416632</t>
-  </si>
-  <si>
-    <t>0.02112906653045293</t>
-  </si>
-  <si>
-    <t>5665.5586</t>
-  </si>
-  <si>
-    <t>6598.104</t>
-  </si>
-  <si>
-    <t>9836.896</t>
-  </si>
-  <si>
-    <t>4085.2458</t>
-  </si>
-  <si>
-    <t>20745.627</t>
-  </si>
-  <si>
-    <t>10169.836</t>
-  </si>
-  <si>
-    <t>16332.766</t>
-  </si>
-  <si>
-    <t>2892.3628</t>
-  </si>
-  <si>
-    <t>1436.7596</t>
-  </si>
-  <si>
-    <t>3002.7314</t>
-  </si>
-  <si>
-    <t>14558.832333333334</t>
-  </si>
-  <si>
-    <t>8030.659266666667</t>
-  </si>
-  <si>
-    <t>2443.951266666667</t>
   </si>
   <si>
     <t>137.1062</t>
@@ -3049,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B27F1D-65F2-4DD8-B808-ECF38C122112}">
-  <dimension ref="A1:GK9"/>
+  <dimension ref="A1:GK6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="10.90625" style="1"/>
@@ -3642,139 +2970,127 @@
     </row>
     <row r="2" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>197</v>
+        <v>372</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>198</v>
+        <v>373</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>199</v>
+        <v>374</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="L2" s="3">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>201</v>
+        <v>376</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>202</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>203</v>
+        <v>377</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>202</v>
+        <v>378</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>203</v>
+        <v>379</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>202</v>
+        <v>380</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>204</v>
+        <v>381</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>205</v>
+        <v>382</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>206</v>
+        <v>383</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>207</v>
+        <v>384</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>208</v>
+        <v>385</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>209</v>
+        <v>386</v>
       </c>
       <c r="BM2" s="3">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="BO2" s="3" t="s">
-        <v>210</v>
+        <v>387</v>
       </c>
       <c r="BP2" s="3" t="s">
-        <v>211</v>
+        <v>388</v>
       </c>
       <c r="BQ2" s="3" t="s">
-        <v>193</v>
+        <v>372</v>
       </c>
       <c r="BR2" s="3" t="s">
-        <v>212</v>
+        <v>389</v>
       </c>
       <c r="BS2" s="3" t="s">
-        <v>213</v>
+        <v>390</v>
       </c>
       <c r="BT2" s="3" t="s">
-        <v>214</v>
+        <v>391</v>
       </c>
       <c r="BU2" s="3" t="s">
-        <v>215</v>
+        <v>392</v>
       </c>
       <c r="BV2" s="3" t="s">
-        <v>216</v>
+        <v>393</v>
       </c>
       <c r="BW2" s="3" t="s">
-        <v>217</v>
+        <v>394</v>
       </c>
       <c r="CC2" s="3" t="s">
-        <v>218</v>
+        <v>395</v>
       </c>
       <c r="CD2" s="3" t="s">
-        <v>219</v>
+        <v>396</v>
       </c>
       <c r="CE2" s="3" t="s">
-        <v>220</v>
+        <v>397</v>
       </c>
       <c r="CF2" s="3" t="s">
-        <v>221</v>
+        <v>398</v>
       </c>
       <c r="CG2" s="3" t="s">
-        <v>222</v>
+        <v>399</v>
       </c>
       <c r="CH2" s="3" t="s">
-        <v>223</v>
+        <v>400</v>
       </c>
       <c r="CI2" s="3" t="s">
-        <v>224</v>
+        <v>401</v>
       </c>
       <c r="CJ2" s="3" t="s">
-        <v>225</v>
+        <v>391</v>
       </c>
       <c r="CK2" s="3" t="s">
-        <v>226</v>
+        <v>402</v>
       </c>
       <c r="CL2" s="3" t="s">
-        <v>227</v>
+        <v>403</v>
       </c>
       <c r="CM2" s="3" t="s">
-        <v>228</v>
+        <v>404</v>
       </c>
       <c r="CN2" s="3" t="s">
-        <v>228</v>
+        <v>405</v>
       </c>
       <c r="CO2" s="3" t="s">
         <v>229</v>
@@ -3783,238 +3099,235 @@
         <v>229</v>
       </c>
       <c r="CQ2" s="3" t="s">
-        <v>230</v>
+        <v>406</v>
       </c>
       <c r="CR2" s="3" t="s">
-        <v>216</v>
+        <v>393</v>
       </c>
       <c r="CS2" s="3">
         <v>1</v>
       </c>
       <c r="CT2" s="3">
-        <v>39803</v>
+        <v>171085</v>
       </c>
       <c r="CU2" s="3" t="s">
-        <v>231</v>
+        <v>407</v>
       </c>
       <c r="CV2" s="3" t="s">
-        <v>232</v>
+        <v>408</v>
       </c>
       <c r="CW2" s="3" t="s">
-        <v>212</v>
+        <v>409</v>
       </c>
       <c r="CX2" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="CY2" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="CZ2" s="3" t="s">
-        <v>235</v>
+        <v>410</v>
       </c>
       <c r="DA2" s="3" t="s">
-        <v>236</v>
+        <v>411</v>
       </c>
       <c r="DB2" s="3">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="DC2" s="3">
-        <v>39803</v>
+        <v>171085</v>
       </c>
       <c r="DD2" s="3" t="s">
-        <v>237</v>
+        <v>412</v>
       </c>
       <c r="DE2" s="3" t="s">
-        <v>238</v>
+        <v>413</v>
       </c>
       <c r="DF2" s="3" t="s">
-        <v>222</v>
+        <v>414</v>
       </c>
       <c r="DG2" s="3" t="s">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="DH2" s="3" t="s">
-        <v>204</v>
+        <v>397</v>
       </c>
       <c r="DI2" s="3" t="s">
-        <v>239</v>
+        <v>416</v>
       </c>
       <c r="DJ2" s="3" t="s">
-        <v>240</v>
+        <v>417</v>
       </c>
       <c r="DK2" s="3" t="s">
-        <v>241</v>
+        <v>418</v>
       </c>
       <c r="DL2" s="3" t="s">
-        <v>242</v>
+        <v>419</v>
       </c>
       <c r="DM2" s="3" t="s">
-        <v>243</v>
+        <v>420</v>
       </c>
       <c r="DN2" s="3" t="s">
-        <v>244</v>
+        <v>421</v>
       </c>
       <c r="DO2" s="3" t="s">
-        <v>245</v>
+        <v>422</v>
       </c>
       <c r="DP2" s="3" t="s">
-        <v>202</v>
+        <v>423</v>
       </c>
       <c r="DQ2" s="3" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="DR2" s="3" t="s">
         <v>202</v>
       </c>
       <c r="DS2" s="3" t="s">
-        <v>247</v>
+        <v>424</v>
       </c>
       <c r="DT2" s="3" t="s">
-        <v>248</v>
+        <v>425</v>
       </c>
       <c r="DU2" s="3" t="s">
-        <v>249</v>
+        <v>425</v>
       </c>
       <c r="DV2" s="3" t="s">
-        <v>250</v>
+        <v>426</v>
       </c>
       <c r="DX2" s="3" t="s">
-        <v>251</v>
+        <v>427</v>
       </c>
       <c r="DY2" s="3" t="s">
-        <v>252</v>
+        <v>428</v>
       </c>
       <c r="DZ2" s="3" t="s">
-        <v>222</v>
+        <v>429</v>
       </c>
       <c r="EA2" s="3" t="s">
-        <v>253</v>
+        <v>430</v>
       </c>
       <c r="EB2" s="3" t="s">
-        <v>254</v>
+        <v>431</v>
       </c>
       <c r="EC2" s="3" t="s">
-        <v>238</v>
+        <v>432</v>
       </c>
       <c r="ED2" s="3" t="s">
-        <v>255</v>
+        <v>433</v>
       </c>
       <c r="EE2" s="3" t="s">
-        <v>256</v>
+        <v>434</v>
       </c>
       <c r="EF2" s="3" t="s">
-        <v>231</v>
+        <v>435</v>
       </c>
       <c r="EG2" s="3" t="s">
-        <v>257</v>
+        <v>436</v>
       </c>
       <c r="EH2" s="3" t="s">
-        <v>258</v>
+        <v>437</v>
       </c>
       <c r="EI2" s="3" t="s">
-        <v>259</v>
+        <v>438</v>
       </c>
       <c r="EJ2" s="3" t="s">
-        <v>260</v>
+        <v>439</v>
       </c>
       <c r="EK2" s="3" t="s">
-        <v>261</v>
+        <v>372</v>
       </c>
       <c r="EL2" s="3" t="s">
-        <v>262</v>
+        <v>440</v>
       </c>
       <c r="EM2" s="3" t="s">
-        <v>263</v>
+        <v>441</v>
       </c>
       <c r="EN2" s="3" t="s">
-        <v>264</v>
+        <v>442</v>
       </c>
       <c r="EO2" s="3" t="s">
-        <v>265</v>
+        <v>443</v>
       </c>
       <c r="EP2" s="3" t="s">
-        <v>265</v>
+        <v>444</v>
       </c>
       <c r="ER2" s="3" t="s">
-        <v>237</v>
+        <v>445</v>
       </c>
       <c r="ES2" s="3" t="s">
-        <v>238</v>
+        <v>432</v>
       </c>
       <c r="ET2" s="3" t="s">
-        <v>222</v>
+        <v>429</v>
       </c>
       <c r="EU2" s="3" t="s">
-        <v>223</v>
+        <v>446</v>
       </c>
       <c r="EV2" s="3" t="s">
-        <v>241</v>
+        <v>447</v>
       </c>
       <c r="EW2" s="3" t="s">
-        <v>242</v>
+        <v>448</v>
       </c>
       <c r="EX2" s="3" t="s">
-        <v>243</v>
+        <v>449</v>
       </c>
       <c r="EY2" s="3" t="s">
-        <v>244</v>
+        <v>450</v>
       </c>
       <c r="EZ2" s="3" t="s">
-        <v>266</v>
+        <v>355</v>
       </c>
       <c r="FA2" s="3" t="s">
-        <v>267</v>
+        <v>451</v>
       </c>
       <c r="FB2" s="3" t="s">
-        <v>268</v>
+        <v>452</v>
       </c>
       <c r="FD2" s="3" t="s">
         <v>269</v>
       </c>
       <c r="FE2" s="3" t="s">
-        <v>270</v>
+        <v>453</v>
       </c>
       <c r="FF2" s="3" t="s">
-        <v>271</v>
+        <v>454</v>
       </c>
       <c r="FH2" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FI2" s="3" t="s">
-        <v>273</v>
+        <v>455</v>
       </c>
       <c r="FJ2" s="3" t="s">
-        <v>274</v>
+        <v>456</v>
       </c>
       <c r="FL2" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FM2" s="3" t="s">
-        <v>198</v>
+        <v>373</v>
       </c>
       <c r="FN2" s="3" t="s">
-        <v>199</v>
+        <v>374</v>
       </c>
       <c r="FY2" s="3" t="s">
-        <v>275</v>
+        <v>457</v>
       </c>
       <c r="FZ2" s="3" t="s">
-        <v>276</v>
+        <v>458</v>
       </c>
       <c r="GA2" s="3" t="s">
-        <v>277</v>
+        <v>459</v>
       </c>
       <c r="GB2" s="3" t="s">
-        <v>278</v>
+        <v>460</v>
       </c>
       <c r="GC2" s="3" t="s">
-        <v>279</v>
+        <v>461</v>
       </c>
       <c r="GD2" s="3" t="s">
-        <v>280</v>
+        <v>462</v>
       </c>
       <c r="GE2" s="3" t="s">
-        <v>281</v>
+        <v>463</v>
       </c>
       <c r="GF2" s="3" t="s">
         <v>251</v>
@@ -4026,10 +3339,10 @@
         <v>251</v>
       </c>
       <c r="GI2" s="3" t="s">
-        <v>282</v>
+        <v>464</v>
       </c>
       <c r="GJ2" s="3" t="s">
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="GK2" s="3" t="s">
         <v>251</v>
@@ -4037,145 +3350,232 @@
     </row>
     <row r="3" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>284</v>
+        <v>541</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>285</v>
+        <v>542</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>286</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>287</v>
+        <v>543</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>288</v>
+        <v>544</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>289</v>
+        <v>545</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>290</v>
+        <v>546</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>291</v>
+        <v>547</v>
       </c>
       <c r="L3" s="3">
-        <v>38</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>251</v>
+        <v>13</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>292</v>
+        <v>548</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>251</v>
+        <v>549</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>292</v>
+        <v>550</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>251</v>
+        <v>551</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>292</v>
+        <v>550</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>251</v>
+        <v>551</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>292</v>
+        <v>204</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>251</v>
+        <v>552</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>292</v>
+        <v>206</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>251</v>
+        <v>553</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>292</v>
+        <v>208</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>251</v>
+        <v>554</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>50</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>11</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="AV3" s="3">
+        <v>67</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="BG3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BH3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="BM3" s="3">
-        <v>352</v>
+        <v>223</v>
+      </c>
+      <c r="BN3" s="3">
+        <v>5</v>
       </c>
       <c r="BO3" s="3" t="s">
-        <v>293</v>
+        <v>578</v>
       </c>
       <c r="BP3" s="3" t="s">
-        <v>294</v>
+        <v>579</v>
       </c>
       <c r="BQ3" s="3" t="s">
-        <v>284</v>
+        <v>541</v>
       </c>
       <c r="BR3" s="3" t="s">
-        <v>295</v>
+        <v>580</v>
       </c>
       <c r="BS3" s="3" t="s">
-        <v>296</v>
+        <v>581</v>
       </c>
       <c r="BT3" s="3" t="s">
-        <v>297</v>
+        <v>582</v>
       </c>
       <c r="BU3" s="3" t="s">
-        <v>298</v>
+        <v>583</v>
       </c>
       <c r="BV3" s="3" t="s">
-        <v>299</v>
+        <v>584</v>
       </c>
       <c r="BW3" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="CC3" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="CD3" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="CE3" s="3" t="s">
-        <v>302</v>
+        <v>585</v>
       </c>
       <c r="CF3" s="3" t="s">
-        <v>303</v>
+        <v>583</v>
       </c>
       <c r="CG3" s="3" t="s">
-        <v>304</v>
+        <v>586</v>
       </c>
       <c r="CH3" s="3" t="s">
-        <v>305</v>
+        <v>587</v>
       </c>
       <c r="CI3" s="3" t="s">
-        <v>306</v>
+        <v>588</v>
       </c>
       <c r="CJ3" s="3" t="s">
-        <v>307</v>
+        <v>589</v>
       </c>
       <c r="CK3" s="3" t="s">
-        <v>308</v>
+        <v>590</v>
       </c>
       <c r="CL3" s="3" t="s">
-        <v>309</v>
+        <v>591</v>
       </c>
       <c r="CM3" s="3" t="s">
-        <v>310</v>
+        <v>592</v>
       </c>
       <c r="CN3" s="3" t="s">
-        <v>311</v>
+        <v>593</v>
       </c>
       <c r="CO3" s="3" t="s">
         <v>229</v>
@@ -4184,82 +3584,82 @@
         <v>229</v>
       </c>
       <c r="CQ3" s="3" t="s">
-        <v>312</v>
+        <v>594</v>
       </c>
       <c r="CR3" s="3" t="s">
-        <v>299</v>
+        <v>584</v>
       </c>
       <c r="CS3" s="3">
         <v>1</v>
       </c>
       <c r="CT3" s="3">
-        <v>119101</v>
+        <v>21353</v>
       </c>
       <c r="CU3" s="3" t="s">
-        <v>313</v>
+        <v>595</v>
       </c>
       <c r="CV3" s="3" t="s">
-        <v>314</v>
+        <v>596</v>
       </c>
       <c r="CW3" s="3" t="s">
-        <v>315</v>
+        <v>597</v>
       </c>
       <c r="CX3" s="3" t="s">
         <v>233</v>
       </c>
       <c r="CY3" s="3" t="s">
-        <v>316</v>
+        <v>598</v>
       </c>
       <c r="CZ3" s="3" t="s">
-        <v>317</v>
+        <v>599</v>
       </c>
       <c r="DA3" s="3" t="s">
-        <v>318</v>
+        <v>600</v>
       </c>
       <c r="DB3" s="3">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="DC3" s="3">
-        <v>119101</v>
+        <v>21353</v>
       </c>
       <c r="DD3" s="3" t="s">
-        <v>319</v>
+        <v>601</v>
       </c>
       <c r="DE3" s="3" t="s">
-        <v>320</v>
+        <v>602</v>
       </c>
       <c r="DF3" s="3" t="s">
-        <v>321</v>
+        <v>603</v>
       </c>
       <c r="DG3" s="3" t="s">
-        <v>322</v>
+        <v>604</v>
       </c>
       <c r="DH3" s="3" t="s">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="DI3" s="3" t="s">
-        <v>219</v>
+        <v>605</v>
       </c>
       <c r="DJ3" s="3" t="s">
-        <v>301</v>
+        <v>606</v>
       </c>
       <c r="DK3" s="3" t="s">
-        <v>323</v>
+        <v>607</v>
       </c>
       <c r="DL3" s="3" t="s">
-        <v>324</v>
+        <v>608</v>
       </c>
       <c r="DM3" s="3" t="s">
-        <v>325</v>
+        <v>609</v>
       </c>
       <c r="DN3" s="3" t="s">
-        <v>326</v>
+        <v>610</v>
       </c>
       <c r="DO3" s="3" t="s">
-        <v>327</v>
+        <v>611</v>
       </c>
       <c r="DP3" s="3" t="s">
-        <v>328</v>
+        <v>612</v>
       </c>
       <c r="DQ3" s="3" t="s">
         <v>229</v>
@@ -4271,151 +3671,151 @@
         <v>329</v>
       </c>
       <c r="DT3" s="3" t="s">
-        <v>330</v>
+        <v>613</v>
       </c>
       <c r="DU3" s="3" t="s">
-        <v>330</v>
+        <v>557</v>
       </c>
       <c r="DV3" s="3" t="s">
-        <v>331</v>
+        <v>558</v>
       </c>
       <c r="DX3" s="3" t="s">
-        <v>332</v>
+        <v>614</v>
       </c>
       <c r="DY3" s="3" t="s">
-        <v>333</v>
+        <v>615</v>
       </c>
       <c r="DZ3" s="3" t="s">
-        <v>334</v>
+        <v>556</v>
       </c>
       <c r="EA3" s="3" t="s">
         <v>253</v>
       </c>
       <c r="EB3" s="3" t="s">
-        <v>335</v>
+        <v>616</v>
       </c>
       <c r="EC3" s="3" t="s">
-        <v>336</v>
+        <v>566</v>
       </c>
       <c r="ED3" s="3" t="s">
-        <v>337</v>
+        <v>617</v>
       </c>
       <c r="EE3" s="3" t="s">
-        <v>338</v>
+        <v>618</v>
       </c>
       <c r="EF3" s="3" t="s">
-        <v>339</v>
+        <v>619</v>
       </c>
       <c r="EG3" s="3" t="s">
-        <v>340</v>
+        <v>620</v>
       </c>
       <c r="EH3" s="3" t="s">
-        <v>341</v>
+        <v>621</v>
       </c>
       <c r="EI3" s="3" t="s">
-        <v>342</v>
+        <v>622</v>
       </c>
       <c r="EJ3" s="3" t="s">
-        <v>343</v>
+        <v>623</v>
       </c>
       <c r="EK3" s="3" t="s">
-        <v>344</v>
+        <v>624</v>
       </c>
       <c r="EL3" s="3" t="s">
-        <v>345</v>
+        <v>625</v>
       </c>
       <c r="EM3" s="3" t="s">
-        <v>346</v>
+        <v>626</v>
       </c>
       <c r="EN3" s="3" t="s">
-        <v>347</v>
+        <v>627</v>
       </c>
       <c r="EO3" s="3" t="s">
-        <v>348</v>
+        <v>628</v>
       </c>
       <c r="EP3" s="3" t="s">
-        <v>348</v>
+        <v>628</v>
       </c>
       <c r="ER3" s="3" t="s">
-        <v>349</v>
+        <v>544</v>
       </c>
       <c r="ES3" s="3" t="s">
-        <v>336</v>
+        <v>566</v>
       </c>
       <c r="ET3" s="3" t="s">
-        <v>334</v>
+        <v>556</v>
       </c>
       <c r="EU3" s="3" t="s">
-        <v>350</v>
+        <v>564</v>
       </c>
       <c r="EV3" s="3" t="s">
-        <v>351</v>
+        <v>629</v>
       </c>
       <c r="EW3" s="3" t="s">
-        <v>352</v>
+        <v>630</v>
       </c>
       <c r="EX3" s="3" t="s">
-        <v>353</v>
+        <v>631</v>
       </c>
       <c r="EY3" s="3" t="s">
-        <v>354</v>
+        <v>632</v>
       </c>
       <c r="EZ3" s="3" t="s">
         <v>355</v>
       </c>
       <c r="FA3" s="3" t="s">
-        <v>356</v>
+        <v>633</v>
       </c>
       <c r="FB3" s="3" t="s">
-        <v>357</v>
+        <v>634</v>
       </c>
       <c r="FD3" s="3" t="s">
         <v>269</v>
       </c>
       <c r="FE3" s="3" t="s">
-        <v>358</v>
+        <v>635</v>
       </c>
       <c r="FF3" s="3" t="s">
-        <v>359</v>
+        <v>636</v>
       </c>
       <c r="FH3" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FI3" s="3" t="s">
-        <v>360</v>
+        <v>637</v>
       </c>
       <c r="FJ3" s="3" t="s">
-        <v>361</v>
+        <v>638</v>
       </c>
       <c r="FL3" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FM3" s="3" t="s">
-        <v>289</v>
+        <v>545</v>
       </c>
       <c r="FN3" s="3" t="s">
-        <v>290</v>
+        <v>546</v>
       </c>
       <c r="FY3" s="3" t="s">
-        <v>362</v>
+        <v>639</v>
       </c>
       <c r="FZ3" s="3" t="s">
-        <v>363</v>
+        <v>640</v>
       </c>
       <c r="GA3" s="3" t="s">
-        <v>364</v>
+        <v>641</v>
       </c>
       <c r="GB3" s="3" t="s">
-        <v>365</v>
+        <v>642</v>
       </c>
       <c r="GC3" s="3" t="s">
-        <v>366</v>
+        <v>643</v>
       </c>
       <c r="GD3" s="3" t="s">
-        <v>367</v>
+        <v>644</v>
       </c>
       <c r="GE3" s="3" t="s">
-        <v>368</v>
+        <v>645</v>
       </c>
       <c r="GF3" s="3" t="s">
         <v>251</v>
@@ -4427,10 +3827,10 @@
         <v>251</v>
       </c>
       <c r="GI3" s="3" t="s">
-        <v>369</v>
+        <v>646</v>
       </c>
       <c r="GJ3" s="3" t="s">
-        <v>370</v>
+        <v>647</v>
       </c>
       <c r="GK3" s="3" t="s">
         <v>251</v>
@@ -4438,256 +3838,379 @@
     </row>
     <row r="4" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>288</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3">
-        <v>288</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>371</v>
+        <v>193</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>372</v>
+        <v>198</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>373</v>
+        <v>199</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>374</v>
+        <v>200</v>
       </c>
       <c r="L4" s="3">
-        <v>37</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>292</v>
+        <v>201</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>292</v>
+        <v>204</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>292</v>
+        <v>206</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>292</v>
+        <v>208</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="BM4" s="3">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="BO4" s="3" t="s">
-        <v>375</v>
+        <v>210</v>
       </c>
       <c r="BP4" s="3" t="s">
-        <v>376</v>
+        <v>211</v>
       </c>
       <c r="BQ4" s="3" t="s">
-        <v>371</v>
+        <v>193</v>
       </c>
       <c r="BR4" s="3" t="s">
-        <v>377</v>
+        <v>212</v>
       </c>
       <c r="BS4" s="3" t="s">
-        <v>378</v>
+        <v>213</v>
       </c>
       <c r="BT4" s="3" t="s">
-        <v>379</v>
+        <v>214</v>
       </c>
       <c r="BU4" s="3" t="s">
-        <v>380</v>
+        <v>215</v>
       </c>
       <c r="BV4" s="3" t="s">
-        <v>381</v>
+        <v>216</v>
       </c>
       <c r="BW4" s="3" t="s">
-        <v>382</v>
+        <v>217</v>
       </c>
       <c r="CC4" s="3" t="s">
-        <v>383</v>
+        <v>218</v>
       </c>
       <c r="CD4" s="3" t="s">
-        <v>384</v>
+        <v>219</v>
       </c>
       <c r="CE4" s="3" t="s">
-        <v>385</v>
+        <v>220</v>
       </c>
       <c r="CF4" s="3" t="s">
-        <v>386</v>
+        <v>221</v>
       </c>
       <c r="CG4" s="3" t="s">
-        <v>387</v>
+        <v>222</v>
       </c>
       <c r="CH4" s="3" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
       <c r="CI4" s="3" t="s">
-        <v>389</v>
+        <v>224</v>
       </c>
       <c r="CJ4" s="3" t="s">
-        <v>390</v>
+        <v>225</v>
+      </c>
+      <c r="CK4" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="CL4" s="3" t="s">
-        <v>391</v>
+        <v>227</v>
       </c>
       <c r="CM4" s="3" t="s">
-        <v>392</v>
+        <v>228</v>
+      </c>
+      <c r="CN4" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="CO4" s="3" t="s">
         <v>229</v>
       </c>
+      <c r="CP4" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="CQ4" s="3" t="s">
-        <v>393</v>
+        <v>230</v>
       </c>
       <c r="CR4" s="3" t="s">
-        <v>381</v>
+        <v>216</v>
       </c>
       <c r="CS4" s="3">
         <v>1</v>
       </c>
       <c r="CT4" s="3">
-        <v>208846</v>
+        <v>39803</v>
       </c>
       <c r="CU4" s="3" t="s">
-        <v>394</v>
+        <v>231</v>
       </c>
       <c r="CV4" s="3" t="s">
-        <v>395</v>
+        <v>232</v>
       </c>
       <c r="CW4" s="3" t="s">
-        <v>396</v>
+        <v>212</v>
       </c>
       <c r="CX4" s="3" t="s">
-        <v>397</v>
+        <v>233</v>
+      </c>
+      <c r="CY4" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="CZ4" s="3" t="s">
-        <v>398</v>
+        <v>235</v>
       </c>
       <c r="DA4" s="3" t="s">
-        <v>399</v>
+        <v>236</v>
       </c>
       <c r="DB4" s="3">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="DC4" s="3">
-        <v>208846</v>
+        <v>39803</v>
       </c>
       <c r="DD4" s="3" t="s">
-        <v>400</v>
+        <v>237</v>
       </c>
       <c r="DE4" s="3" t="s">
-        <v>401</v>
+        <v>238</v>
       </c>
       <c r="DF4" s="3" t="s">
-        <v>402</v>
+        <v>222</v>
       </c>
       <c r="DG4" s="3" t="s">
-        <v>403</v>
+        <v>223</v>
       </c>
       <c r="DH4" s="3" t="s">
-        <v>404</v>
+        <v>204</v>
       </c>
       <c r="DI4" s="3" t="s">
-        <v>405</v>
+        <v>239</v>
       </c>
       <c r="DJ4" s="3" t="s">
-        <v>406</v>
+        <v>240</v>
       </c>
       <c r="DK4" s="3" t="s">
-        <v>407</v>
+        <v>241</v>
       </c>
       <c r="DL4" s="3" t="s">
-        <v>408</v>
+        <v>242</v>
+      </c>
+      <c r="DM4" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="DN4" s="3" t="s">
-        <v>409</v>
+        <v>244</v>
       </c>
       <c r="DO4" s="3" t="s">
-        <v>410</v>
+        <v>245</v>
+      </c>
+      <c r="DP4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="DQ4" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="DR4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="DS4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="DT4" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="DU4" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="DV4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="DX4" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="DY4" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="DZ4" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="EA4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="EB4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="EC4" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="ED4" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="EE4" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="EF4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="EG4" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="EH4" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="EI4" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="EK4" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="EL4" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="EM4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="EN4" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="EO4" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="EP4" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="ER4" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="ES4" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="ET4" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="EU4" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="EV4" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="EW4" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="EX4" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="EY4" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="EZ4" s="3" t="s">
-        <v>355</v>
+        <v>266</v>
       </c>
       <c r="FA4" s="3" t="s">
-        <v>411</v>
+        <v>267</v>
       </c>
       <c r="FB4" s="3" t="s">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="FD4" s="3" t="s">
         <v>269</v>
       </c>
       <c r="FE4" s="3" t="s">
-        <v>413</v>
+        <v>270</v>
       </c>
       <c r="FF4" s="3" t="s">
-        <v>414</v>
+        <v>271</v>
       </c>
       <c r="FH4" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FI4" s="3" t="s">
-        <v>415</v>
+        <v>273</v>
       </c>
       <c r="FJ4" s="3" t="s">
-        <v>416</v>
+        <v>274</v>
       </c>
       <c r="FL4" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FM4" s="3" t="s">
-        <v>372</v>
+        <v>198</v>
       </c>
       <c r="FN4" s="3" t="s">
-        <v>373</v>
+        <v>199</v>
       </c>
       <c r="FY4" s="3" t="s">
-        <v>417</v>
+        <v>275</v>
       </c>
       <c r="FZ4" s="3" t="s">
-        <v>418</v>
+        <v>276</v>
       </c>
       <c r="GA4" s="3" t="s">
-        <v>419</v>
+        <v>277</v>
       </c>
       <c r="GB4" s="3" t="s">
-        <v>420</v>
+        <v>278</v>
       </c>
       <c r="GC4" s="3" t="s">
-        <v>421</v>
+        <v>279</v>
       </c>
       <c r="GD4" s="3" t="s">
-        <v>422</v>
+        <v>280</v>
       </c>
       <c r="GE4" s="3" t="s">
-        <v>423</v>
+        <v>281</v>
       </c>
       <c r="GF4" s="3" t="s">
         <v>251</v>
@@ -4696,141 +4219,159 @@
         <v>251</v>
       </c>
       <c r="GH4" s="3" t="s">
-        <v>424</v>
+        <v>251</v>
       </c>
       <c r="GI4" s="3" t="s">
-        <v>425</v>
+        <v>282</v>
       </c>
       <c r="GJ4" s="3" t="s">
-        <v>426</v>
+        <v>283</v>
       </c>
       <c r="GK4" s="3" t="s">
-        <v>427</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>428</v>
+        <v>284</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>429</v>
+        <v>289</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>430</v>
+        <v>290</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>431</v>
+        <v>291</v>
       </c>
       <c r="L5" s="3">
-        <v>123</v>
+        <v>38</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>432</v>
+        <v>292</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>433</v>
+        <v>292</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>434</v>
+        <v>251</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>435</v>
+        <v>292</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>436</v>
+        <v>251</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>437</v>
+        <v>292</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>438</v>
+        <v>251</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>439</v>
+        <v>292</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>440</v>
+        <v>251</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>441</v>
+        <v>292</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>442</v>
+        <v>251</v>
       </c>
       <c r="BM5" s="3">
-        <v>90</v>
+        <v>352</v>
       </c>
       <c r="BO5" s="3" t="s">
-        <v>443</v>
+        <v>293</v>
       </c>
       <c r="BP5" s="3" t="s">
-        <v>444</v>
+        <v>294</v>
       </c>
       <c r="BQ5" s="3" t="s">
-        <v>428</v>
+        <v>284</v>
       </c>
       <c r="BR5" s="3" t="s">
-        <v>445</v>
+        <v>295</v>
       </c>
       <c r="BS5" s="3" t="s">
-        <v>446</v>
+        <v>296</v>
       </c>
       <c r="BT5" s="3" t="s">
-        <v>447</v>
+        <v>297</v>
       </c>
       <c r="BU5" s="3" t="s">
-        <v>448</v>
+        <v>298</v>
       </c>
       <c r="BV5" s="3" t="s">
-        <v>449</v>
+        <v>299</v>
       </c>
       <c r="BW5" s="3" t="s">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="CC5" s="3" t="s">
-        <v>451</v>
+        <v>301</v>
       </c>
       <c r="CD5" s="3" t="s">
-        <v>452</v>
+        <v>219</v>
       </c>
       <c r="CE5" s="3" t="s">
-        <v>453</v>
+        <v>302</v>
       </c>
       <c r="CF5" s="3" t="s">
-        <v>454</v>
+        <v>303</v>
       </c>
       <c r="CG5" s="3" t="s">
-        <v>455</v>
+        <v>304</v>
       </c>
       <c r="CH5" s="3" t="s">
-        <v>456</v>
+        <v>305</v>
       </c>
       <c r="CI5" s="3" t="s">
-        <v>457</v>
+        <v>306</v>
       </c>
       <c r="CJ5" s="3" t="s">
-        <v>447</v>
+        <v>307</v>
       </c>
       <c r="CK5" s="3" t="s">
-        <v>458</v>
+        <v>308</v>
       </c>
       <c r="CL5" s="3" t="s">
-        <v>459</v>
+        <v>309</v>
       </c>
       <c r="CM5" s="3" t="s">
-        <v>460</v>
+        <v>310</v>
       </c>
       <c r="CN5" s="3" t="s">
-        <v>461</v>
+        <v>311</v>
       </c>
       <c r="CO5" s="3" t="s">
         <v>229</v>
@@ -4839,79 +4380,82 @@
         <v>229</v>
       </c>
       <c r="CQ5" s="3" t="s">
-        <v>462</v>
+        <v>312</v>
       </c>
       <c r="CR5" s="3" t="s">
-        <v>449</v>
+        <v>299</v>
       </c>
       <c r="CS5" s="3">
         <v>1</v>
       </c>
       <c r="CT5" s="3">
-        <v>171085</v>
+        <v>119101</v>
       </c>
       <c r="CU5" s="3" t="s">
-        <v>463</v>
+        <v>313</v>
       </c>
       <c r="CV5" s="3" t="s">
-        <v>464</v>
+        <v>314</v>
       </c>
       <c r="CW5" s="3" t="s">
-        <v>465</v>
+        <v>315</v>
       </c>
       <c r="CX5" s="3" t="s">
         <v>233</v>
       </c>
+      <c r="CY5" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="CZ5" s="3" t="s">
-        <v>466</v>
+        <v>317</v>
       </c>
       <c r="DA5" s="3" t="s">
-        <v>467</v>
+        <v>318</v>
       </c>
       <c r="DB5" s="3">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="DC5" s="3">
-        <v>171085</v>
+        <v>119101</v>
       </c>
       <c r="DD5" s="3" t="s">
-        <v>468</v>
+        <v>319</v>
       </c>
       <c r="DE5" s="3" t="s">
-        <v>469</v>
+        <v>320</v>
       </c>
       <c r="DF5" s="3" t="s">
-        <v>470</v>
+        <v>321</v>
       </c>
       <c r="DG5" s="3" t="s">
-        <v>471</v>
+        <v>322</v>
       </c>
       <c r="DH5" s="3" t="s">
-        <v>453</v>
+        <v>302</v>
       </c>
       <c r="DI5" s="3" t="s">
-        <v>472</v>
+        <v>219</v>
       </c>
       <c r="DJ5" s="3" t="s">
-        <v>473</v>
+        <v>301</v>
       </c>
       <c r="DK5" s="3" t="s">
-        <v>474</v>
+        <v>323</v>
       </c>
       <c r="DL5" s="3" t="s">
-        <v>475</v>
+        <v>324</v>
       </c>
       <c r="DM5" s="3" t="s">
-        <v>476</v>
+        <v>325</v>
       </c>
       <c r="DN5" s="3" t="s">
-        <v>477</v>
+        <v>326</v>
       </c>
       <c r="DO5" s="3" t="s">
-        <v>478</v>
+        <v>327</v>
       </c>
       <c r="DP5" s="3" t="s">
-        <v>479</v>
+        <v>328</v>
       </c>
       <c r="DQ5" s="3" t="s">
         <v>229</v>
@@ -4920,154 +4464,154 @@
         <v>202</v>
       </c>
       <c r="DS5" s="3" t="s">
-        <v>480</v>
+        <v>329</v>
       </c>
       <c r="DT5" s="3" t="s">
-        <v>481</v>
+        <v>330</v>
       </c>
       <c r="DU5" s="3" t="s">
-        <v>481</v>
+        <v>330</v>
       </c>
       <c r="DV5" s="3" t="s">
-        <v>482</v>
+        <v>331</v>
       </c>
       <c r="DX5" s="3" t="s">
-        <v>483</v>
+        <v>332</v>
       </c>
       <c r="DY5" s="3" t="s">
-        <v>484</v>
+        <v>333</v>
       </c>
       <c r="DZ5" s="3" t="s">
-        <v>485</v>
+        <v>334</v>
       </c>
       <c r="EA5" s="3" t="s">
-        <v>486</v>
+        <v>253</v>
       </c>
       <c r="EB5" s="3" t="s">
-        <v>487</v>
+        <v>335</v>
       </c>
       <c r="EC5" s="3" t="s">
-        <v>488</v>
+        <v>336</v>
       </c>
       <c r="ED5" s="3" t="s">
-        <v>489</v>
+        <v>337</v>
       </c>
       <c r="EE5" s="3" t="s">
-        <v>490</v>
+        <v>338</v>
       </c>
       <c r="EF5" s="3" t="s">
-        <v>491</v>
+        <v>339</v>
       </c>
       <c r="EG5" s="3" t="s">
-        <v>492</v>
+        <v>340</v>
       </c>
       <c r="EH5" s="3" t="s">
-        <v>493</v>
+        <v>341</v>
       </c>
       <c r="EI5" s="3" t="s">
-        <v>494</v>
+        <v>342</v>
       </c>
       <c r="EJ5" s="3" t="s">
-        <v>495</v>
+        <v>343</v>
       </c>
       <c r="EK5" s="3" t="s">
-        <v>428</v>
+        <v>344</v>
       </c>
       <c r="EL5" s="3" t="s">
-        <v>496</v>
+        <v>345</v>
       </c>
       <c r="EM5" s="3" t="s">
-        <v>497</v>
+        <v>346</v>
       </c>
       <c r="EN5" s="3" t="s">
-        <v>498</v>
+        <v>347</v>
       </c>
       <c r="EO5" s="3" t="s">
-        <v>499</v>
+        <v>348</v>
       </c>
       <c r="EP5" s="3" t="s">
-        <v>500</v>
+        <v>348</v>
       </c>
       <c r="ER5" s="3" t="s">
-        <v>501</v>
+        <v>349</v>
       </c>
       <c r="ES5" s="3" t="s">
-        <v>488</v>
+        <v>336</v>
       </c>
       <c r="ET5" s="3" t="s">
-        <v>485</v>
+        <v>334</v>
       </c>
       <c r="EU5" s="3" t="s">
-        <v>502</v>
+        <v>350</v>
       </c>
       <c r="EV5" s="3" t="s">
-        <v>503</v>
+        <v>351</v>
       </c>
       <c r="EW5" s="3" t="s">
-        <v>504</v>
+        <v>352</v>
       </c>
       <c r="EX5" s="3" t="s">
-        <v>505</v>
+        <v>353</v>
       </c>
       <c r="EY5" s="3" t="s">
-        <v>506</v>
+        <v>354</v>
       </c>
       <c r="EZ5" s="3" t="s">
         <v>355</v>
       </c>
       <c r="FA5" s="3" t="s">
-        <v>507</v>
+        <v>356</v>
       </c>
       <c r="FB5" s="3" t="s">
-        <v>508</v>
+        <v>357</v>
       </c>
       <c r="FD5" s="3" t="s">
         <v>269</v>
       </c>
       <c r="FE5" s="3" t="s">
-        <v>509</v>
+        <v>358</v>
       </c>
       <c r="FF5" s="3" t="s">
-        <v>510</v>
+        <v>359</v>
       </c>
       <c r="FH5" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FI5" s="3" t="s">
-        <v>511</v>
+        <v>360</v>
       </c>
       <c r="FJ5" s="3" t="s">
-        <v>512</v>
+        <v>361</v>
       </c>
       <c r="FL5" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FM5" s="3" t="s">
-        <v>429</v>
+        <v>289</v>
       </c>
       <c r="FN5" s="3" t="s">
-        <v>430</v>
+        <v>290</v>
       </c>
       <c r="FY5" s="3" t="s">
-        <v>513</v>
+        <v>362</v>
       </c>
       <c r="FZ5" s="3" t="s">
-        <v>514</v>
+        <v>363</v>
       </c>
       <c r="GA5" s="3" t="s">
-        <v>515</v>
+        <v>364</v>
       </c>
       <c r="GB5" s="3" t="s">
-        <v>516</v>
+        <v>365</v>
       </c>
       <c r="GC5" s="3" t="s">
-        <v>517</v>
+        <v>366</v>
       </c>
       <c r="GD5" s="3" t="s">
-        <v>518</v>
+        <v>367</v>
       </c>
       <c r="GE5" s="3" t="s">
-        <v>519</v>
+        <v>368</v>
       </c>
       <c r="GF5" s="3" t="s">
         <v>251</v>
@@ -5079,10 +4623,10 @@
         <v>251</v>
       </c>
       <c r="GI5" s="3" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="GJ5" s="3" t="s">
-        <v>521</v>
+        <v>370</v>
       </c>
       <c r="GK5" s="3" t="s">
         <v>251</v>
@@ -5090,124 +4634,133 @@
     </row>
     <row r="6" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>571</v>
+        <v>604</v>
       </c>
       <c r="B6" s="3">
-        <v>571</v>
+        <v>604</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>522</v>
+        <v>470</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>523</v>
+        <v>471</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>524</v>
+        <v>472</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>525</v>
+        <v>473</v>
       </c>
       <c r="L6" s="3">
-        <v>169</v>
+        <v>82</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>475</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>526</v>
+        <v>474</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>527</v>
+        <v>475</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>528</v>
+        <v>474</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>527</v>
+        <v>475</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>529</v>
+        <v>474</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>531</v>
+        <v>474</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>532</v>
+        <v>474</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>533</v>
+        <v>474</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="BM6" s="3">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="BO6" s="3" t="s">
-        <v>534</v>
+        <v>476</v>
       </c>
       <c r="BP6" s="3" t="s">
-        <v>535</v>
+        <v>477</v>
       </c>
       <c r="BQ6" s="3" t="s">
-        <v>536</v>
+        <v>470</v>
       </c>
       <c r="BR6" s="3" t="s">
-        <v>537</v>
+        <v>478</v>
       </c>
       <c r="BS6" s="3" t="s">
-        <v>538</v>
+        <v>479</v>
       </c>
       <c r="BT6" s="3" t="s">
-        <v>539</v>
+        <v>480</v>
       </c>
       <c r="BU6" s="3" t="s">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="BV6" s="3" t="s">
-        <v>541</v>
+        <v>482</v>
       </c>
       <c r="BW6" s="3" t="s">
-        <v>542</v>
+        <v>483</v>
       </c>
       <c r="CC6" s="3" t="s">
-        <v>543</v>
+        <v>468</v>
       </c>
       <c r="CD6" s="3" t="s">
-        <v>544</v>
+        <v>467</v>
       </c>
       <c r="CE6" s="3" t="s">
-        <v>302</v>
+        <v>466</v>
       </c>
       <c r="CF6" s="3" t="s">
-        <v>545</v>
+        <v>484</v>
       </c>
       <c r="CG6" s="3" t="s">
-        <v>546</v>
+        <v>485</v>
       </c>
       <c r="CH6" s="3" t="s">
-        <v>547</v>
+        <v>486</v>
       </c>
       <c r="CI6" s="3" t="s">
-        <v>548</v>
+        <v>487</v>
       </c>
       <c r="CJ6" s="3" t="s">
-        <v>549</v>
+        <v>488</v>
+      </c>
+      <c r="CK6" s="3" t="s">
+        <v>489</v>
       </c>
       <c r="CL6" s="3" t="s">
-        <v>550</v>
+        <v>490</v>
       </c>
       <c r="CM6" s="3" t="s">
-        <v>551</v>
+        <v>491</v>
       </c>
       <c r="CN6" s="3" t="s">
-        <v>552</v>
+        <v>492</v>
       </c>
       <c r="CO6" s="3" t="s">
         <v>229</v>
@@ -5216,76 +4769,73 @@
         <v>229</v>
       </c>
       <c r="CQ6" s="3" t="s">
-        <v>553</v>
+        <v>493</v>
       </c>
       <c r="CR6" s="3" t="s">
-        <v>541</v>
+        <v>482</v>
       </c>
       <c r="CS6" s="3">
         <v>1</v>
       </c>
       <c r="CT6" s="3">
-        <v>213687</v>
+        <v>213316</v>
       </c>
       <c r="CU6" s="3" t="s">
-        <v>554</v>
+        <v>494</v>
       </c>
       <c r="CV6" s="3" t="s">
-        <v>555</v>
+        <v>495</v>
       </c>
       <c r="CW6" s="3" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="CX6" s="3" t="s">
         <v>233</v>
       </c>
       <c r="CZ6" s="3" t="s">
-        <v>557</v>
+        <v>496</v>
       </c>
       <c r="DA6" s="3" t="s">
-        <v>558</v>
+        <v>497</v>
       </c>
       <c r="DB6" s="3">
-        <v>570</v>
+        <v>603</v>
       </c>
       <c r="DC6" s="3">
-        <v>213687</v>
+        <v>213316</v>
       </c>
       <c r="DD6" s="3" t="s">
-        <v>554</v>
+        <v>494</v>
       </c>
       <c r="DE6" s="3" t="s">
-        <v>559</v>
+        <v>498</v>
       </c>
       <c r="DF6" s="3" t="s">
-        <v>560</v>
+        <v>485</v>
       </c>
       <c r="DG6" s="3" t="s">
-        <v>561</v>
+        <v>486</v>
       </c>
       <c r="DH6" s="3" t="s">
-        <v>531</v>
+        <v>466</v>
       </c>
       <c r="DI6" s="3" t="s">
-        <v>562</v>
+        <v>467</v>
       </c>
       <c r="DJ6" s="3" t="s">
-        <v>563</v>
+        <v>468</v>
       </c>
       <c r="DK6" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="DL6" s="3" t="s">
-        <v>565</v>
+        <v>251</v>
       </c>
       <c r="DN6" s="3" t="s">
-        <v>566</v>
+        <v>469</v>
       </c>
       <c r="DO6" s="3" t="s">
-        <v>567</v>
+        <v>499</v>
       </c>
       <c r="DP6" s="3" t="s">
-        <v>568</v>
+        <v>500</v>
       </c>
       <c r="DQ6" s="3" t="s">
         <v>229</v>
@@ -5294,1417 +4844,178 @@
         <v>202</v>
       </c>
       <c r="DS6" s="3" t="s">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="DT6" s="3" t="s">
-        <v>569</v>
+        <v>501</v>
       </c>
       <c r="DU6" s="3" t="s">
-        <v>569</v>
+        <v>501</v>
       </c>
       <c r="DV6" s="3" t="s">
-        <v>570</v>
+        <v>502</v>
       </c>
       <c r="DX6" s="3" t="s">
-        <v>202</v>
+        <v>503</v>
       </c>
       <c r="DY6" s="3" t="s">
-        <v>571</v>
+        <v>504</v>
       </c>
       <c r="DZ6" s="3" t="s">
-        <v>572</v>
+        <v>505</v>
       </c>
       <c r="EA6" s="3" t="s">
         <v>253</v>
       </c>
       <c r="EB6" s="3" t="s">
-        <v>573</v>
+        <v>506</v>
       </c>
       <c r="EC6" s="3" t="s">
-        <v>574</v>
+        <v>507</v>
       </c>
       <c r="ED6" s="3" t="s">
-        <v>575</v>
+        <v>508</v>
       </c>
       <c r="EE6" s="3" t="s">
-        <v>576</v>
+        <v>509</v>
       </c>
       <c r="EF6" s="3" t="s">
-        <v>577</v>
+        <v>510</v>
       </c>
       <c r="EG6" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="EH6" s="3">
-        <v>139650361</v>
+        <v>511</v>
+      </c>
+      <c r="EH6" s="3" t="s">
+        <v>512</v>
       </c>
       <c r="EI6" s="3" t="s">
-        <v>579</v>
+        <v>513</v>
       </c>
       <c r="EJ6" s="3" t="s">
-        <v>329</v>
+        <v>514</v>
       </c>
       <c r="EK6" s="3" t="s">
-        <v>580</v>
+        <v>515</v>
       </c>
       <c r="EL6" s="3" t="s">
-        <v>581</v>
+        <v>516</v>
       </c>
       <c r="EM6" s="3" t="s">
-        <v>582</v>
+        <v>517</v>
       </c>
       <c r="EN6" s="3" t="s">
-        <v>583</v>
+        <v>518</v>
       </c>
       <c r="EO6" s="3" t="s">
-        <v>584</v>
+        <v>519</v>
       </c>
       <c r="EP6" s="3" t="s">
-        <v>584</v>
+        <v>520</v>
       </c>
       <c r="ER6" s="3" t="s">
-        <v>585</v>
+        <v>521</v>
       </c>
       <c r="ES6" s="3" t="s">
-        <v>574</v>
+        <v>507</v>
       </c>
       <c r="ET6" s="3" t="s">
-        <v>572</v>
+        <v>505</v>
       </c>
       <c r="EU6" s="3" t="s">
-        <v>586</v>
+        <v>522</v>
       </c>
       <c r="EV6" s="3" t="s">
-        <v>251</v>
+        <v>523</v>
+      </c>
+      <c r="EW6" s="3" t="s">
+        <v>524</v>
       </c>
       <c r="EY6" s="3" t="s">
-        <v>587</v>
+        <v>525</v>
       </c>
       <c r="EZ6" s="3" t="s">
         <v>355</v>
       </c>
       <c r="FA6" s="3" t="s">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="FB6" s="3" t="s">
-        <v>589</v>
+        <v>527</v>
       </c>
       <c r="FD6" s="3" t="s">
         <v>269</v>
       </c>
       <c r="FE6" s="3" t="s">
-        <v>590</v>
+        <v>528</v>
       </c>
       <c r="FF6" s="3" t="s">
-        <v>591</v>
+        <v>529</v>
       </c>
       <c r="FH6" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FI6" s="3" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="FJ6" s="3" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="FL6" s="3" t="s">
         <v>272</v>
       </c>
       <c r="FM6" s="3" t="s">
-        <v>523</v>
+        <v>471</v>
       </c>
       <c r="FN6" s="3" t="s">
-        <v>524</v>
+        <v>472</v>
+      </c>
+      <c r="FR6" s="3">
+        <v>57</v>
       </c>
       <c r="FY6" s="3" t="s">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="FZ6" s="3" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="GA6" s="3" t="s">
-        <v>596</v>
+        <v>534</v>
       </c>
       <c r="GB6" s="3" t="s">
-        <v>597</v>
+        <v>535</v>
       </c>
       <c r="GC6" s="3" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="GD6" s="3" t="s">
-        <v>599</v>
+        <v>537</v>
       </c>
       <c r="GE6" s="3" t="s">
-        <v>600</v>
+        <v>538</v>
       </c>
       <c r="GF6" s="3" t="s">
-        <v>601</v>
+        <v>251</v>
       </c>
       <c r="GG6" s="3" t="s">
-        <v>602</v>
+        <v>251</v>
       </c>
       <c r="GH6" s="3" t="s">
-        <v>603</v>
+        <v>251</v>
       </c>
       <c r="GI6" s="3" t="s">
-        <v>604</v>
+        <v>539</v>
       </c>
       <c r="GJ6" s="3" t="s">
-        <v>605</v>
+        <v>540</v>
       </c>
       <c r="GK6" s="3" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="7" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>604</v>
-      </c>
-      <c r="B7" s="3">
-        <v>604</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="L7" s="3">
-        <v>82</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="Z7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="BM7" s="3">
-        <v>39</v>
-      </c>
-      <c r="BO7" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="BP7" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="BQ7" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="BR7" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="BS7" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="BT7" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="BU7" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="BV7" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="BW7" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="CC7" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="CD7" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="CE7" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="CF7" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="CG7" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="CH7" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="CI7" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="CJ7" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="CK7" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="CL7" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="CM7" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="CN7" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="CO7" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="CP7" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="CQ7" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="CR7" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="CS7" s="3">
-        <v>1</v>
-      </c>
-      <c r="CT7" s="3">
-        <v>213316</v>
-      </c>
-      <c r="CU7" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="CV7" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="CW7" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="CX7" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="CZ7" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="DA7" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="DB7" s="3">
-        <v>603</v>
-      </c>
-      <c r="DC7" s="3">
-        <v>213316</v>
-      </c>
-      <c r="DD7" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="DE7" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="DF7" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="DG7" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="DH7" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="DI7" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="DJ7" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="DK7" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="DN7" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="DO7" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="DP7" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="DQ7" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="DR7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="DS7" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="DT7" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="DU7" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="DV7" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="DX7" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="DY7" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="DZ7" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="EA7" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="EB7" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="EC7" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="ED7" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="EE7" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="EF7" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="EG7" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="EH7" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="EI7" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="EJ7" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="EK7" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="EL7" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="EM7" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="EN7" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="EO7" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="EP7" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="ER7" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="ES7" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="ET7" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="EU7" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="EV7" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="EW7" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="EY7" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="EZ7" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="FA7" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="FB7" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="FD7" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="FE7" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="FF7" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="FH7" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="FI7" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="FJ7" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="FL7" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="FM7" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="FN7" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="FR7" s="3">
-        <v>57</v>
-      </c>
-      <c r="FY7" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="FZ7" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="GA7" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="GB7" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="GC7" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="GD7" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="GE7" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="GF7" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="GG7" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="GH7" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="GI7" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="GJ7" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="GK7" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="8" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>78</v>
-      </c>
-      <c r="B8" s="3">
-        <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="L8" s="3">
-        <v>24</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="BM8" s="3">
-        <v>237</v>
-      </c>
-      <c r="BO8" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="BP8" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="BQ8" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="BR8" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="BS8" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="BT8" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="BU8" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="BV8" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="BW8" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="CC8" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="CD8" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="CE8" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="CF8" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="CG8" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="CH8" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="CI8" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="CJ8" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="CK8" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="CL8" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="CM8" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="CN8" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="CO8" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="CP8" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="CQ8" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="CR8" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="CS8" s="3">
-        <v>1</v>
-      </c>
-      <c r="CT8" s="3">
-        <v>20838</v>
-      </c>
-      <c r="CU8" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="CV8" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="CW8" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="CX8" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="CY8" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="CZ8" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="DA8" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="DB8" s="3">
-        <v>77</v>
-      </c>
-      <c r="DC8" s="3">
-        <v>20838</v>
-      </c>
-      <c r="DD8" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="DE8" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="DF8" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="DG8" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="DH8" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="DK8" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="DL8" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="DM8" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="DN8" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="DO8" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="DP8" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="DQ8" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="DR8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="DS8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="DT8" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="DU8" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="DV8" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="DX8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="DY8" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="DZ8" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="EA8" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="EB8" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="EC8" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="ED8" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="EE8" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="EF8" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="EG8" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="EH8" s="3">
-        <v>88680875</v>
-      </c>
-      <c r="EI8" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="EJ8" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="EK8" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="EL8" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="EM8" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="EN8" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="EO8" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="EP8" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="ER8" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="ES8" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="ET8" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="EU8" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="EV8" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="EW8" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="EX8" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="EY8" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="EZ8" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="FA8" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="FB8" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="FD8" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="FE8" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="FF8" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="FH8" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="FI8" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="FJ8" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="FL8" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="FM8" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="FN8" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="FR8" s="3">
-        <v>6</v>
-      </c>
-      <c r="FY8" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="FZ8" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="GA8" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="GB8" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="GC8" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="GD8" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="GE8" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="GF8" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="GG8" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="GH8" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="GI8" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="GJ8" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="GK8" s="3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="9" spans="1:193" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>94</v>
-      </c>
-      <c r="B9" s="3">
-        <v>94</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="L9" s="3">
-        <v>13</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>50</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="AI9" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="AJ9" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="AK9" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="AM9" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="AN9" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="AO9" s="3">
-        <v>11</v>
-      </c>
-      <c r="AP9" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="AQ9" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="AR9" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="AS9" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="AT9" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="AU9" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="AV9" s="3">
-        <v>67</v>
-      </c>
-      <c r="AW9" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="AX9" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="AY9" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="AZ9" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="BA9" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="BB9" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="BC9" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="BD9" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="BE9" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="BF9" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="BG9" s="3">
-        <v>1</v>
-      </c>
-      <c r="BH9" s="3">
-        <v>1</v>
-      </c>
-      <c r="BI9" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="BJ9" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="BK9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="BL9" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="BM9" s="3">
-        <v>223</v>
-      </c>
-      <c r="BN9" s="3">
-        <v>5</v>
-      </c>
-      <c r="BO9" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="BP9" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="BQ9" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="BR9" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="BS9" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="BT9" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="BU9" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="BV9" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="BW9" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="CF9" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="CG9" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="CH9" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="CI9" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="CJ9" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="CK9" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="CL9" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="CM9" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="CN9" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="CO9" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="CP9" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="CQ9" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="CR9" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="CS9" s="3">
-        <v>1</v>
-      </c>
-      <c r="CT9" s="3">
-        <v>21353</v>
-      </c>
-      <c r="CU9" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="CV9" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="CW9" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="CX9" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="CY9" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="CZ9" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="DA9" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="DB9" s="3">
-        <v>93</v>
-      </c>
-      <c r="DC9" s="3">
-        <v>21353</v>
-      </c>
-      <c r="DD9" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="DE9" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="DF9" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="DG9" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="DH9" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="DI9" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="DJ9" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="DK9" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="DL9" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="DM9" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="DN9" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="DO9" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="DP9" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="DQ9" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="DR9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="DS9" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="DT9" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="DU9" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="DV9" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="DX9" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="DY9" s="3" t="s">
-        <v>839</v>
-      </c>
-      <c r="DZ9" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="EA9" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="EB9" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="EC9" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="ED9" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="EE9" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="EF9" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="EG9" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="EH9" s="3" t="s">
-        <v>845</v>
-      </c>
-      <c r="EI9" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="EJ9" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="EK9" s="3" t="s">
-        <v>848</v>
-      </c>
-      <c r="EL9" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="EM9" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="EN9" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="EO9" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="EP9" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="ER9" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="ES9" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="ET9" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="EU9" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="EV9" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="EW9" s="3" t="s">
-        <v>854</v>
-      </c>
-      <c r="EX9" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="EY9" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="EZ9" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="FA9" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="FB9" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="FD9" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="FE9" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="FF9" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="FH9" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="FI9" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="FJ9" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="FL9" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="FM9" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="FN9" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="FY9" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="FZ9" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="GA9" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="GB9" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="GC9" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="GD9" s="3" t="s">
-        <v>868</v>
-      </c>
-      <c r="GE9" s="3" t="s">
-        <v>869</v>
-      </c>
-      <c r="GF9" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="GG9" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="GH9" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="GI9" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="GJ9" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="GK9" s="3" t="s">
         <v>251</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:GK6">
+    <sortCondition ref="A2:A6"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>